--- a/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,83</t>
+          <t>2,8; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,08</t>
+          <t>4,37; 9,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,86</t>
+          <t>2,73; 7,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 14,28</t>
+          <t>8,55; 14,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,45</t>
+          <t>3,25; 8,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 12,64</t>
+          <t>5,26; 12,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,75</t>
+          <t>3,23; 8,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,71</t>
+          <t>7,08; 11,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,55</t>
+          <t>3,36; 6,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,67</t>
+          <t>5,47; 10,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,82</t>
+          <t>3,34; 6,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,47</t>
+          <t>8,68; 12,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,54</t>
+          <t>3,47; 8,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,9</t>
+          <t>4,56; 10,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,44</t>
+          <t>3,34; 8,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,66</t>
+          <t>6,97; 12,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,51</t>
+          <t>3,59; 8,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,11</t>
+          <t>5,24; 10,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,02</t>
+          <t>3,2; 8,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,83</t>
+          <t>6,99; 11,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,46</t>
+          <t>4,0; 7,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,39</t>
+          <t>5,44; 9,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,24</t>
+          <t>3,98; 7,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,42</t>
+          <t>7,74; 11,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,53</t>
+          <t>4,5; 8,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 14,96</t>
+          <t>9,05; 14,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,32</t>
+          <t>5,37; 10,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 17,17</t>
+          <t>3,72; 17,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 16,17</t>
+          <t>5,77; 15,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 14,12</t>
+          <t>6,37; 13,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,65</t>
+          <t>4,35; 14,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 20,15</t>
+          <t>10,27; 19,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,21</t>
+          <t>5,39; 9,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,66</t>
+          <t>9,21; 13,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,4</t>
+          <t>5,85; 10,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 16,3</t>
+          <t>5,29; 16,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,58</t>
+          <t>6,49; 9,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 13,17</t>
+          <t>9,23; 13,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,22</t>
+          <t>6,01; 9,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,9</t>
+          <t>12,5; 17,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,47</t>
+          <t>6,02; 10,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,71</t>
+          <t>10,68; 15,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,05</t>
+          <t>6,85; 10,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 65,73</t>
+          <t>11,27; 63,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 9,38</t>
+          <t>6,74; 9,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 13,39</t>
+          <t>10,31; 13,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,26</t>
+          <t>6,9; 9,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 43,58</t>
+          <t>12,81; 51,2</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,43</t>
+          <t>5,16; 11,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,47</t>
+          <t>6,59; 11,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,09</t>
+          <t>6,47; 11,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 24,75</t>
+          <t>16,93; 24,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,52</t>
+          <t>6,47; 11,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,35; 16,45</t>
+          <t>11,54; 16,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,52</t>
+          <t>8,58; 13,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,5; 18,49</t>
+          <t>11,0; 18,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,42</t>
+          <t>6,49; 10,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 13,94</t>
+          <t>10,18; 13,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,91</t>
+          <t>8,23; 11,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 19,77</t>
+          <t>14,04; 19,7</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,82</t>
+          <t>2,6; 7,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 12,46</t>
+          <t>5,07; 12,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,21</t>
+          <t>4,15; 10,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,99</t>
+          <t>2,81; 10,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,8</t>
+          <t>7,43; 10,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,34</t>
+          <t>9,48; 13,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,38</t>
+          <t>7,52; 11,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,65; 21,13</t>
+          <t>16,59; 21,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,62</t>
+          <t>6,7; 9,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,57</t>
+          <t>8,97; 12,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,34</t>
+          <t>7,28; 10,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,68; 17,99</t>
+          <t>13,63; 17,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,59</t>
+          <t>5,87; 7,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 10,74</t>
+          <t>8,51; 10,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,03</t>
+          <t>6,13; 7,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 14,35</t>
+          <t>9,87; 14,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,0</t>
+          <t>7,14; 9,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 12,64</t>
+          <t>10,39; 12,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,81</t>
+          <t>7,82; 9,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,42; 34,29</t>
+          <t>13,43; 33,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,03</t>
+          <t>6,69; 8,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 11,32</t>
+          <t>9,77; 11,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,55</t>
+          <t>7,25; 8,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,86; 23,7</t>
+          <t>12,87; 23,93</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12919; 32276</t>
+          <t>13247; 32613</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18655; 44072</t>
+          <t>19100; 43392</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11943; 29003</t>
+          <t>11551; 29675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43872; 71384</t>
+          <t>42732; 71523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10197; 25924</t>
+          <t>9972; 25911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17593; 39742</t>
+          <t>16540; 39795</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11800; 30356</t>
+          <t>11212; 29806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30957; 52067</t>
+          <t>31464; 53177</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26629; 51047</t>
+          <t>26223; 51974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40534; 72658</t>
+          <t>41127; 75416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26753; 52455</t>
+          <t>25734; 50797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>82129; 117789</t>
+          <t>81987; 118791</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12825; 31157</t>
+          <t>12671; 31478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18177; 41466</t>
+          <t>19087; 42643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13127; 31829</t>
+          <t>12604; 31241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32208; 57008</t>
+          <t>31381; 56484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12589; 31547</t>
+          <t>13300; 31894</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16336; 37454</t>
+          <t>17661; 36518</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11913; 29761</t>
+          <t>11864; 30223</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26692; 45060</t>
+          <t>26634; 45085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28914; 54904</t>
+          <t>29397; 55868</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41106; 71013</t>
+          <t>41089; 72004</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28250; 54173</t>
+          <t>29758; 53861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64047; 94915</t>
+          <t>64365; 95502</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23835; 46181</t>
+          <t>24360; 47436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57506; 94176</t>
+          <t>56985; 94342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28316; 53873</t>
+          <t>28027; 53258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23285; 114641</t>
+          <t>24840; 116554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10338; 26808</t>
+          <t>9564; 25482</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17443; 36587</t>
+          <t>16511; 35997</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7204; 24333</t>
+          <t>7226; 23758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17432; 33506</t>
+          <t>17077; 32972</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39636; 65157</t>
+          <t>38152; 67201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80454; 121342</t>
+          <t>81882; 123724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40259; 71543</t>
+          <t>40251; 70449</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32082; 135925</t>
+          <t>44126; 136548</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81027; 118300</t>
+          <t>80145; 117919</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105537; 152621</t>
+          <t>106954; 154284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67298; 105673</t>
+          <t>68902; 105879</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129661; 174067</t>
+          <t>128733; 175641</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43067; 74759</t>
+          <t>43022; 72370</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81285; 120455</t>
+          <t>81916; 118248</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56595; 91171</t>
+          <t>56496; 90290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>107113; 640373</t>
+          <t>109751; 615600</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>135107; 182793</t>
+          <t>131343; 182320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>198998; 257937</t>
+          <t>198470; 257511</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134690; 182489</t>
+          <t>135960; 185073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>257671; 873400</t>
+          <t>256676; 1026051</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18960; 39983</t>
+          <t>18038; 40836</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32759; 58345</t>
+          <t>33521; 58840</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40499; 68267</t>
+          <t>39832; 70641</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79274; 115761</t>
+          <t>79189; 115088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37235; 65519</t>
+          <t>36798; 64039</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86457; 125239</t>
+          <t>87897; 127715</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64734; 99374</t>
+          <t>63106; 100203</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96170; 154610</t>
+          <t>91968; 153221</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60112; 95725</t>
+          <t>59647; 94372</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129489; 176996</t>
+          <t>129310; 174913</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114637; 160921</t>
+          <t>111117; 159951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>183862; 257841</t>
+          <t>183078; 256818</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7917; 23245</t>
+          <t>7714; 23539</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13556; 33125</t>
+          <t>13473; 32883</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11769; 29132</t>
+          <t>11854; 28964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6905; 26229</t>
+          <t>6703; 26037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92978; 134775</t>
+          <t>92732; 133952</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>103524; 147969</t>
+          <t>105217; 147397</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81610; 122924</t>
+          <t>81215; 123524</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>126695; 160786</t>
+          <t>126281; 161323</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>104196; 148667</t>
+          <t>103499; 145972</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124626; 172811</t>
+          <t>123340; 169520</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100398; 141120</t>
+          <t>99352; 143753</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136714; 179790</t>
+          <t>136263; 178559</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>190953; 247634</t>
+          <t>191496; 250241</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>292312; 367146</t>
+          <t>290954; 363168</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209909; 270500</t>
+          <t>206418; 267480</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>346400; 481146</t>
+          <t>331111; 482274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>240406; 303709</t>
+          <t>240748; 303850</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368047; 448571</t>
+          <t>368714; 449364</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>274639; 345842</t>
+          <t>275496; 345040</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>478256; 1221838</t>
+          <t>478668; 1184307</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>445998; 532825</t>
+          <t>444082; 535894</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>684186; 788610</t>
+          <t>680547; 787899</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>500382; 589512</t>
+          <t>499763; 593881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>889277; 1639100</t>
+          <t>890530; 1655057</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,9</t>
+          <t>2,89; 6,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,92</t>
+          <t>4,21; 9,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,02</t>
+          <t>2,67; 6,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 14,31</t>
+          <t>8,65; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,45</t>
+          <t>3,19; 8,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,66</t>
+          <t>5,43; 12,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,59</t>
+          <t>3,43; 8,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,96</t>
+          <t>7,07; 11,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,67</t>
+          <t>3,48; 6,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,03</t>
+          <t>5,52; 9,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,6</t>
+          <t>3,55; 6,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 12,58</t>
+          <t>8,4; 12,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,63</t>
+          <t>3,38; 8,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,18</t>
+          <t>4,42; 9,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,28</t>
+          <t>3,42; 8,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 12,54</t>
+          <t>6,95; 12,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,6</t>
+          <t>3,65; 8,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,83</t>
+          <t>4,96; 11,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,14</t>
+          <t>3,15; 8,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,84</t>
+          <t>7,2; 11,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,59</t>
+          <t>4,19; 7,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,53</t>
+          <t>5,41; 9,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,2</t>
+          <t>3,98; 7,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,49</t>
+          <t>7,73; 11,39</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,76</t>
+          <t>4,66; 8,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,99</t>
+          <t>9,07; 14,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,2</t>
+          <t>5,65; 10,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 17,46</t>
+          <t>12,32; 18,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,37</t>
+          <t>5,92; 15,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,89</t>
+          <t>6,83; 14,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,3</t>
+          <t>4,39; 13,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 19,83</t>
+          <t>10,58; 19,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,5</t>
+          <t>5,59; 9,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,92</t>
+          <t>9,11; 13,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,24</t>
+          <t>6,05; 9,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,38</t>
+          <t>12,61; 17,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,55</t>
+          <t>6,64; 9,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,31</t>
+          <t>9,21; 12,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,23</t>
+          <t>6,07; 9,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,06</t>
+          <t>12,6; 16,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,13</t>
+          <t>6,31; 10,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 15,42</t>
+          <t>10,41; 15,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,94</t>
+          <t>7,02; 10,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 63,19</t>
+          <t>10,27; 13,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,35</t>
+          <t>6,81; 9,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,31; 13,37</t>
+          <t>10,13; 13,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,39</t>
+          <t>6,78; 9,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 51,2</t>
+          <t>12,16; 14,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,68</t>
+          <t>5,6; 11,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,57</t>
+          <t>6,42; 11,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,48</t>
+          <t>6,58; 11,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 24,6</t>
+          <t>14,69; 21,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,26</t>
+          <t>6,28; 10,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,77</t>
+          <t>11,35; 16,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,63</t>
+          <t>8,96; 13,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,0; 18,32</t>
+          <t>15,99; 20,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,28</t>
+          <t>6,7; 10,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,77</t>
+          <t>10,05; 13,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,84</t>
+          <t>8,45; 11,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 19,7</t>
+          <t>16,19; 19,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,92</t>
+          <t>2,57; 8,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,37</t>
+          <t>5,08; 12,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,15</t>
+          <t>4,24; 9,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,91</t>
+          <t>4,24; 12,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,74</t>
+          <t>7,31; 10,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,29</t>
+          <t>9,61; 13,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,44</t>
+          <t>7,53; 11,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,59; 21,2</t>
+          <t>16,37; 21,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,45</t>
+          <t>6,77; 9,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,33</t>
+          <t>8,86; 12,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,53</t>
+          <t>7,29; 10,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,86</t>
+          <t>13,97; 18,41</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,67</t>
+          <t>5,81; 7,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,62</t>
+          <t>8,36; 10,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,94</t>
+          <t>6,21; 7,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,38</t>
+          <t>12,24; 14,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,01</t>
+          <t>7,08; 9,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 12,66</t>
+          <t>10,37; 12,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,79</t>
+          <t>7,71; 9,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,43; 33,24</t>
+          <t>13,26; 15,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,08</t>
+          <t>6,76; 8,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 11,31</t>
+          <t>9,75; 11,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,62</t>
+          <t>7,26; 8,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 23,93</t>
+          <t>13,15; 14,7</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98143</t>
+          <t>104100</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13247; 32613</t>
+          <t>13676; 31776</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19100; 43392</t>
+          <t>18410; 42599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11551; 29675</t>
+          <t>11300; 28744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42732; 71523</t>
+          <t>46971; 76031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9972; 25911</t>
+          <t>9784; 25372</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16540; 39795</t>
+          <t>17079; 40037</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11212; 29806</t>
+          <t>11912; 30395</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31464; 53177</t>
+          <t>34309; 55825</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26223; 51974</t>
+          <t>27143; 51176</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41127; 75416</t>
+          <t>41479; 73841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25734; 50797</t>
+          <t>27305; 50927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81987; 118791</t>
+          <t>86422; 124273</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77871</t>
+          <t>83622</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12671; 31478</t>
+          <t>12327; 30434</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19087; 42643</t>
+          <t>18513; 40381</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12604; 31241</t>
+          <t>12919; 31042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31381; 56484</t>
+          <t>33436; 60440</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13300; 31894</t>
+          <t>13537; 32665</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17661; 36518</t>
+          <t>16707; 37870</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11864; 30223</t>
+          <t>11681; 29993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26634; 45085</t>
+          <t>30328; 49799</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29397; 55868</t>
+          <t>30800; 56470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41089; 72004</t>
+          <t>40871; 70723</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29758; 53861</t>
+          <t>29781; 55553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64365; 95502</t>
+          <t>69753; 102763</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92417</t>
+          <t>98908</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24360; 47436</t>
+          <t>25251; 47231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56985; 94342</t>
+          <t>57088; 92075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28027; 53258</t>
+          <t>29470; 54121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24840; 116554</t>
+          <t>58022; 88576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9564; 25482</t>
+          <t>9810; 25645</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16511; 35997</t>
+          <t>17698; 37109</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7226; 23758</t>
+          <t>7289; 23003</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17077; 32972</t>
+          <t>19768; 36832</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38152; 67201</t>
+          <t>39525; 66491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81882; 123724</t>
+          <t>80994; 121742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40251; 70449</t>
+          <t>41604; 68644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44126; 136548</t>
+          <t>82936; 117860</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150806</t>
+          <t>165998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>100914</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>445257</t>
+          <t>266913</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80145; 117919</t>
+          <t>82023; 119585</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106954; 154284</t>
+          <t>106788; 149843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68902; 105879</t>
+          <t>69649; 106070</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128733; 175641</t>
+          <t>141734; 190721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43022; 72370</t>
+          <t>45072; 74756</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81916; 118248</t>
+          <t>79772; 118301</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56496; 90290</t>
+          <t>57916; 89563</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>109751; 615600</t>
+          <t>88003; 118781</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131343; 182320</t>
+          <t>132701; 182701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>198470; 257511</t>
+          <t>194983; 257918</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>135960; 185073</t>
+          <t>133682; 185815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>256676; 1026051</t>
+          <t>240952; 297153</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95548</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>131350</t>
+          <t>148764</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>226898</t>
+          <t>249379</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18038; 40836</t>
+          <t>19590; 40786</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33521; 58840</t>
+          <t>32649; 57773</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39832; 70641</t>
+          <t>40494; 69634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79189; 115088</t>
+          <t>82413; 121483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36798; 64039</t>
+          <t>35736; 61947</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87897; 127715</t>
+          <t>86405; 126015</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63106; 100203</t>
+          <t>65884; 101531</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91968; 153221</t>
+          <t>131956; 165312</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59647; 94372</t>
+          <t>61507; 96051</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129310; 174913</t>
+          <t>127695; 174581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111117; 159951</t>
+          <t>114121; 161288</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>183078; 256818</t>
+          <t>224480; 274289</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>142297</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>156432</t>
+          <t>174408</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7714; 23539</t>
+          <t>7637; 23985</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13473; 32883</t>
+          <t>13501; 34093</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11854; 28964</t>
+          <t>12111; 28369</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6703; 26037</t>
+          <t>9978; 29923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92732; 133952</t>
+          <t>91154; 130574</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105217; 147397</t>
+          <t>106590; 148093</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81215; 123524</t>
+          <t>81334; 120851</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>126281; 161323</t>
+          <t>138190; 177640</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>103499; 145972</t>
+          <t>104513; 146901</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123340; 169520</t>
+          <t>121793; 170247</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99352; 143753</t>
+          <t>99497; 144726</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136263; 178559</t>
+          <t>150732; 198663</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>428427</t>
+          <t>460953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>668590</t>
+          <t>516377</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1097018</t>
+          <t>977329</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>191496; 250241</t>
+          <t>189376; 245098</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>290954; 363168</t>
+          <t>285729; 361184</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206418; 267480</t>
+          <t>209350; 268737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>331111; 482274</t>
+          <t>418093; 502916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>240748; 303850</t>
+          <t>239019; 303769</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368714; 449364</t>
+          <t>367982; 445819</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>275496; 345040</t>
+          <t>271651; 345873</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>478668; 1184307</t>
+          <t>479840; 551331</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>444082; 535894</t>
+          <t>448514; 536783</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>680547; 787899</t>
+          <t>679038; 788821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>499763; 593881</t>
+          <t>500204; 597027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>890530; 1655057</t>
+          <t>925435; 1034024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
